--- a/data/trans_camb/IMC_inf_MED_R2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_MED_R2-Estudios-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,99; 15,55</t>
+          <t>-17,83; 17,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-34,67; 22,39</t>
+          <t>-31,67; 21,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,63; 18,38</t>
+          <t>-13,53; 18,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-32,65; 8,58</t>
+          <t>-30,85; 11,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,78; 11,27</t>
+          <t>-11,99; 10,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-25,68; 8,37</t>
+          <t>-23,77; 10,55</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-32,0; 36,57</t>
+          <t>-32,39; 40,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-66,09; 51,68</t>
+          <t>-60,88; 47,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-23,45; 44,69</t>
+          <t>-25,05; 45,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-57,69; 22,55</t>
+          <t>-57,42; 27,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-21,8; 24,7</t>
+          <t>-20,59; 23,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-47,69; 18,62</t>
+          <t>-44,54; 22,28</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,23; -3,39</t>
+          <t>-16,11; -3,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-31,67; -11,34</t>
+          <t>-30,91; -10,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,7; -4,0</t>
+          <t>-16,36; -4,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,83; -0,66</t>
+          <t>-16,73; -0,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,27; -5,67</t>
+          <t>-14,4; -6,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-22,53; -6,6</t>
+          <t>-21,67; -7,26</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-33,58; -7,76</t>
+          <t>-33,39; -8,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-67,62; -26,78</t>
+          <t>-66,39; -25,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-28,01; -8,11</t>
+          <t>-28,37; -7,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-29,33; -1,25</t>
+          <t>-29,5; -1,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,35; -11,76</t>
+          <t>-27,84; -12,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-44,32; -14,03</t>
+          <t>-42,7; -14,9</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-22,56; -1,75</t>
+          <t>-22,58; -2,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-26,41; -2,57</t>
+          <t>-25,51; -1,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,72; 3,19</t>
+          <t>-19,06; 2,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-35,31; -10,47</t>
+          <t>-36,41; -11,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-17,17; -1,35</t>
+          <t>-17,7; -2,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-26,96; -10,14</t>
+          <t>-27,16; -11,06</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-48,09; -5,19</t>
+          <t>-48,37; -6,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-55,65; -6,1</t>
+          <t>-56,32; -5,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-31,98; 6,82</t>
+          <t>-32,59; 5,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-62,13; -21,05</t>
+          <t>-63,6; -22,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-33,45; -2,67</t>
+          <t>-34,38; -5,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-53,8; -23,32</t>
+          <t>-53,57; -24,19</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-15,41; -5,42</t>
+          <t>-15,21; -5,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-27,0; -10,81</t>
+          <t>-26,6; -10,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,08; -2,95</t>
+          <t>-13,14; -3,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-18,69; -6,21</t>
+          <t>-18,6; -5,67</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,91; -5,71</t>
+          <t>-12,74; -5,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-20,52; -9,8</t>
+          <t>-19,91; -9,56</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-32,92; -12,81</t>
+          <t>-32,32; -12,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-57,31; -24,57</t>
+          <t>-57,62; -23,8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-23,87; -5,91</t>
+          <t>-23,71; -6,65</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-34,2; -12,17</t>
+          <t>-33,18; -10,88</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-25,15; -11,97</t>
+          <t>-24,64; -11,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-41,73; -20,4</t>
+          <t>-39,17; -19,66</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IMC_inf_MED_R2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_MED_R2-Estudios-trans_camb.xlsx
@@ -513,7 +513,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad observado</t>
+          <t>Menores con sobrepeso u obesidad (IMC recogido por medición)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,83; 17,43</t>
+          <t>-19,76; 13,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-31,67; 21,02</t>
+          <t>-31,03; 23,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,53; 18,95</t>
+          <t>-14,52; 18,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-30,85; 11,46</t>
+          <t>-30,83; 9,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,99; 10,66</t>
+          <t>-10,84; 12,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-23,77; 10,55</t>
+          <t>-24,3; 9,04</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-32,39; 40,1</t>
+          <t>-34,09; 30,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-60,88; 47,04</t>
+          <t>-58,95; 52,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-25,05; 45,15</t>
+          <t>-25,33; 44,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-57,42; 27,2</t>
+          <t>-55,9; 20,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-20,59; 23,23</t>
+          <t>-19,7; 28,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-44,54; 22,28</t>
+          <t>-45,62; 21,16</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,11; -3,54</t>
+          <t>-16,26; -3,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-30,91; -10,89</t>
+          <t>-33,23; -11,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,36; -4,12</t>
+          <t>-16,51; -4,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,73; -0,72</t>
+          <t>-16,76; -0,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,4; -6,2</t>
+          <t>-14,4; -5,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-21,67; -7,26</t>
+          <t>-22,98; -7,84</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-33,39; -8,39</t>
+          <t>-34,41; -8,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-66,39; -25,05</t>
+          <t>-68,84; -27,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-28,37; -7,9</t>
+          <t>-28,85; -7,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-29,5; -1,37</t>
+          <t>-29,58; -0,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,84; -12,9</t>
+          <t>-27,15; -12,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-42,7; -14,9</t>
+          <t>-45,35; -15,98</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-22,58; -2,3</t>
+          <t>-23,0; -2,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-25,51; -1,52</t>
+          <t>-25,79; -1,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-19,06; 2,42</t>
+          <t>-17,68; 2,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-36,41; -11,21</t>
+          <t>-35,0; -12,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-17,7; -2,41</t>
+          <t>-17,03; -2,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-27,16; -11,06</t>
+          <t>-26,99; -9,9</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-48,37; -6,1</t>
+          <t>-48,99; -6,76</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-56,32; -5,35</t>
+          <t>-54,49; -4,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-32,59; 5,09</t>
+          <t>-31,71; 5,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-63,6; -22,91</t>
+          <t>-60,27; -23,39</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-34,38; -5,46</t>
+          <t>-33,98; -4,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-53,57; -24,19</t>
+          <t>-52,7; -22,12</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-15,21; -5,1</t>
+          <t>-15,64; -5,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-26,6; -10,36</t>
+          <t>-26,36; -10,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,14; -3,3</t>
+          <t>-13,21; -3,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-18,6; -5,67</t>
+          <t>-19,34; -6,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,74; -5,38</t>
+          <t>-13,09; -5,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-19,91; -9,56</t>
+          <t>-20,6; -9,98</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-32,32; -12,23</t>
+          <t>-32,68; -12,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-57,62; -23,8</t>
+          <t>-56,64; -23,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-23,71; -6,65</t>
+          <t>-23,41; -5,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-33,18; -10,88</t>
+          <t>-35,09; -12,39</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,64; -11,24</t>
+          <t>-25,46; -11,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-39,17; -19,66</t>
+          <t>-40,97; -20,56</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IMC_inf_MED_R2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_MED_R2-Estudios-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,39</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-7,75</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-2,03</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-6,04</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,39</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-10,72</t>
+          <t>-22,34</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-8,71</t>
+          <t>-13,71</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-19,76; 13,65</t>
+          <t>-13,63; 18,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-31,03; 23,65</t>
+          <t>-30,19; 13,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,52; 18,19</t>
+          <t>-17,99; 15,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-30,83; 9,85</t>
+          <t>-41,35; 1,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,84; 12,64</t>
+          <t>-12,78; 11,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,3; 9,04</t>
+          <t>-28,62; 0,11</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4,72%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-15,31%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-3,97%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-11,83%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>4,72%</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-21,2%</t>
+          <t>-43,73%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-17,12%</t>
+          <t>-26,97%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-34,09; 30,27</t>
+          <t>-23,45; 44,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-58,95; 52,56</t>
+          <t>-53,77; 28,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-25,33; 44,05</t>
+          <t>-32,0; 36,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-55,9; 20,46</t>
+          <t>-76,92; 3,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-19,7; 28,06</t>
+          <t>-21,8; 24,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-45,62; 21,16</t>
+          <t>-52,99; 1,26</t>
         </is>
       </c>
     </row>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-10,23</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-9,49</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-9,92</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-19,87</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-10,23</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-9,07</t>
+          <t>-17,24</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-13,65</t>
+          <t>-12,36</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,26; -3,44</t>
+          <t>-15,7; -4,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-33,23; -11,93</t>
+          <t>-17,5; -1,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,51; -4,0</t>
+          <t>-16,23; -3,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,76; -0,35</t>
+          <t>-24,05; -9,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,4; -5,9</t>
+          <t>-14,27; -5,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-22,98; -7,84</t>
+          <t>-18,08; -6,22</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-18,74%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-17,39%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-22,15%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-44,38%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-18,74%</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-16,62%</t>
+          <t>-38,51%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-27,37%</t>
+          <t>-24,77%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-34,41; -8,62</t>
+          <t>-28,01; -8,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-68,84; -27,49</t>
+          <t>-30,36; -2,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-28,85; -7,79</t>
+          <t>-33,58; -7,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-29,58; -0,92</t>
+          <t>-50,89; -22,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,15; -12,0</t>
+          <t>-27,35; -11,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-45,35; -15,98</t>
+          <t>-34,83; -12,82</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-7,61</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-23,76</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-12,72</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-14,23</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-7,61</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-24,02</t>
+          <t>-14,14</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-19,13</t>
+          <t>-18,97</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-23,0; -2,61</t>
+          <t>-18,72; 3,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-25,79; -1,96</t>
+          <t>-35,48; -10,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,68; 2,64</t>
+          <t>-22,56; -1,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-35,0; -12,05</t>
+          <t>-26,04; -2,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-17,03; -2,17</t>
+          <t>-17,17; -1,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-26,99; -9,9</t>
+          <t>-26,84; -9,94</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-14,39%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-44,93%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-30,0%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-33,57%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-14,39%</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-45,42%</t>
+          <t>-33,37%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-40,14%</t>
+          <t>-39,8%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-48,99; -6,76</t>
+          <t>-31,98; 6,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-54,49; -4,53</t>
+          <t>-62,37; -21,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-31,71; 5,43</t>
+          <t>-48,09; -5,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-60,27; -23,39</t>
+          <t>-55,21; -6,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-33,98; -4,98</t>
+          <t>-33,45; -2,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-52,7; -22,12</t>
+          <t>-53,74; -22,78</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-8,39</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-12,67</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-10,25</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-17,69</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-8,39</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-12,7</t>
+          <t>-17,22</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-14,66</t>
+          <t>-14,29</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-15,64; -5,22</t>
+          <t>-13,08; -2,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-26,36; -10,38</t>
+          <t>-18,76; -6,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,21; -3,01</t>
+          <t>-15,41; -5,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-19,34; -6,55</t>
+          <t>-22,88; -10,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-13,09; -5,49</t>
+          <t>-12,91; -5,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-20,6; -9,98</t>
+          <t>-18,78; -9,7</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-15,61%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-23,56%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-22,77%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-39,28%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-15,61%</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-23,63%</t>
+          <t>-38,23%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-29,63%</t>
+          <t>-28,88%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-32,68; -12,41</t>
+          <t>-23,87; -5,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-56,64; -23,98</t>
+          <t>-34,36; -12,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-23,41; -5,97</t>
+          <t>-32,92; -12,81</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-35,09; -12,39</t>
+          <t>-48,54; -23,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-25,46; -11,48</t>
+          <t>-25,15; -11,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-40,97; -20,56</t>
+          <t>-37,03; -19,93</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IMC_inf_MED_R2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_MED_R2-Estudios-trans_camb.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -118,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -131,6 +134,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -497,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -513,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con sobrepeso u obesidad (IMC recogido por medición)</t>
+          <t>Menores con sobrepeso u obesidad, recogido por medición</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -591,467 +600,319 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2,39</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-7,75</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-2,03</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-22,34</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,4</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-13,71</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>2.388476588246902</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-7.745040207914805</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-2.029375845901971</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-22.34303143522873</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.3956868038808015</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-13.71261707489081</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-13,63; 18,38</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-30,19; 13,15</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-17,99; 15,55</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-41,35; 1,08</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-12,78; 11,27</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-28,62; 0,11</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-13.63255299901299</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-30.18580827977055</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-17.98852419766354</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-41.35278768154758</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-12.77926536179368</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-28.61703024800142</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>4,72%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-15,31%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-3,97%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-43,73%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-26,97%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>18.37758312556035</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>13.15196640156252</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>15.54748888892567</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>1.084287172849319</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>11.26756779700776</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0.107282638458759</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-23,45; 44,69</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-53,77; 28,91</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-32,0; 36,57</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-76,92; 3,61</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-21,8; 24,7</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-52,99; 1,26</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>0.04722515386418637</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-0.1531355665376433</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-0.03972248021487828</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.4373367436685006</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.007781237037007051</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.2696605568114392</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-10,23</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-9,49</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-9,92</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-17,24</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-10,16</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-12,36</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>-0.2345485712024603</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.5377223271889696</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.3200152731120219</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.7692143503745028</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.2179954262602369</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.5299233884982861</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-15,7; -4,0</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-17,5; -1,28</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-16,23; -3,39</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-24,05; -9,88</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-14,27; -5,67</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-18,08; -6,22</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>0.4468720182974343</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.2891072016351949</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.3657325384642078</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.03608061184325247</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.2470432166930881</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.01264105452836701</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n"/>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-18,74%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-17,39%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-22,15%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-38,51%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-20,37%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-24,77%</t>
-        </is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>-10.22977594714139</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-9.491095626764828</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-9.916492826413048</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-17.24162460175855</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-10.16119400565093</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-12.36013269677786</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-28,01; -8,11</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-30,36; -2,35</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-33,58; -7,76</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-50,89; -22,86</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-27,35; -11,76</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-34,83; -12,82</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-15.70197596281848</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-17.49875586310411</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-16.23195960796362</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-24.05417742507901</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-14.27290778062123</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-18.08260311179781</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-7,61</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-23,76</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-12,72</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-14,14</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-9,95</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-18,97</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>-4.000376586760974</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>-1.284970466871025</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>-3.392458528922234</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>-9.883902513915206</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>-5.67343292262395</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>-6.217136865222046</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-18,72; 3,19</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-35,48; -10,72</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-22,56; -1,75</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-26,04; -2,51</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-17,17; -1,35</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-26,84; -9,94</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>-0.1874354894981128</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-0.1739009890214828</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.2214858217580708</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.3850933450174213</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.2036506305793707</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.2477217555676677</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-14,39%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-44,93%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-30,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-33,37%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-20,87%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-39,8%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>-0.2800839536070972</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.3036301343995843</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.335771249555151</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.508876701436594</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.2735183167357972</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.3482704303248685</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-31,98; 6,82</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-62,37; -21,58</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-48,09; -5,19</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-55,21; -6,16</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-33,45; -2,67</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-53,74; -22,78</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>-0.08108628331450166</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>-0.02345659761489161</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>-0.07760648436282587</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>-0.2286483413558958</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>-0.1175882916795651</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>-0.1282189479149009</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1059,153 +920,317 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-8,39</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-12,67</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-10,25</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-17,22</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-9,22</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-14,29</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>-7.610050152512465</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-23.75876352064948</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-12.71822701762091</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-14.14471555302154</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-9.946138391701902</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-18.96886265521468</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-13,08; -2,95</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-18,76; -6,19</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-15,41; -5,42</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-22,88; -10,29</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-12,91; -5,71</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-18,78; -9,7</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-18.71928173642811</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-35.4779983254945</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-22.5607162130729</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-26.04059599049608</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-17.17018843119912</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-26.84499736029849</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>-15,61%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-23,56%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-22,77%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-38,23%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-18,64%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-28,88%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>3.186342780286502</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>-10.71646260846286</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>-1.745389706153557</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>-2.514145062443085</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>-1.353250599069958</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>-9.94453613078675</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>-23,87; -5,91</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>-34,36; -12,25</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>-32,92; -12,81</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>-48,54; -23,89</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>-25,15; -11,97</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-37,03; -19,93</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>-0.1439182569480047</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-0.4493163336121799</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.3000294687673161</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-0.3336810616258132</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.2086935155335914</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.398011617905231</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>-0.3198176715701634</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.6237125194410268</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.4808562558655038</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.5520725370335484</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.3345177886532594</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.537363985895559</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>0.06822991952877665</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>-0.215779748429904</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>-0.05194880300806898</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>-0.06155024915157736</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>-0.02672042714669766</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>-0.2277833883068105</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-8.391661179470066</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-12.66656231669381</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-10.25460147098062</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-17.22004337494615</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-9.222914364735846</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-14.29230862135718</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-13.07779820245377</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-18.75993225146343</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-15.40815857156266</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-22.8758099286172</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-12.90848333589963</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-18.78266628656673</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>-2.950330811214615</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>-6.187606656587176</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>-5.419832303612407</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>-10.2878553892248</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>-5.712606164043647</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>-9.696161862916217</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n"/>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>-0.1561113057524038</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-0.2356379196399032</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-0.2276652148271062</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.3823068975799315</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.1863526481968759</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.2887817727789596</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>-0.2387043366567352</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-0.3436109249951637</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-0.329164891411815</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.4853599544127974</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.2515365723429265</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.3702867044997458</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>-0.05911705144765615</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>-0.122518135302151</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>-0.1280573769471604</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>-0.2389020887040406</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>-0.119731746597375</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>-0.1993494072630917</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1213,14 +1238,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="A4:A9"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="A10:A15"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_camb/IMC_inf_MED_R2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_MED_R2-Estudios-trans_camb.xlsx
@@ -601,22 +601,22 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>2.388476588246902</v>
+        <v>0.7664347599701249</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>-7.745040207914805</v>
+        <v>-3.739154263233679</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>-2.029375845901971</v>
+        <v>-3.591201140527489</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-22.34303143522873</v>
+        <v>-14.77618625213113</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.3956868038808015</v>
+        <v>-1.312173486971285</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>-13.71261707489081</v>
+        <v>-8.758037263058377</v>
       </c>
     </row>
     <row r="5">
@@ -627,22 +627,22 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>-13.63255299901299</v>
+        <v>-13.65651866971792</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>-30.18580827977055</v>
+        <v>-25.90501989986937</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>-17.98852419766354</v>
+        <v>-18.02964357379561</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>-41.35278768154758</v>
+        <v>-33.34006892772985</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-12.77926536179368</v>
+        <v>-11.27219106655301</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>-28.61703024800142</v>
+        <v>-22.35271403585251</v>
       </c>
     </row>
     <row r="6">
@@ -653,22 +653,22 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>18.37758312556035</v>
+        <v>15.13683549927799</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>13.15196640156252</v>
+        <v>16.66257888824369</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>15.54748888892567</v>
+        <v>10.70844778425915</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>1.084287172849319</v>
+        <v>8.275195551062458</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>11.26756779700776</v>
+        <v>9.228563401562258</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0.107282638458759</v>
+        <v>5.549395058913882</v>
       </c>
     </row>
     <row r="7">
@@ -679,22 +679,22 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.04722515386418637</v>
+        <v>0.01645752387005818</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>-0.1531355665376433</v>
+        <v>-0.08029022658549145</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>-0.03972248021487828</v>
+        <v>-0.07371530752753309</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-0.4373367436685006</v>
+        <v>-0.3033055156303394</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.007781237037007051</v>
+        <v>-0.0275222850864013</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.2696605568114392</v>
+        <v>-0.1836961352630144</v>
       </c>
     </row>
     <row r="8">
@@ -705,22 +705,22 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>-0.2345485712024603</v>
+        <v>-0.2529955730025037</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>-0.5377223271889696</v>
+        <v>-0.4996739135616585</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>-0.3200152731120219</v>
+        <v>-0.3354686032579801</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>-0.7692143503745028</v>
+        <v>-0.6364164219400633</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.2179954262602369</v>
+        <v>-0.2173652147291018</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.5299233884982861</v>
+        <v>-0.4370894994921946</v>
       </c>
     </row>
     <row r="9">
@@ -731,22 +731,22 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0.4468720182974343</v>
+        <v>0.3848491511049558</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.2891072016351949</v>
+        <v>0.3971523815395649</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>0.3657325384642078</v>
+        <v>0.2525214879826502</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.03608061184325247</v>
+        <v>0.206156472654267</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.2470432166930881</v>
+        <v>0.2158694779682646</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.01264105452836701</v>
+        <v>0.1314501450048093</v>
       </c>
     </row>
     <row r="10">
@@ -761,22 +761,22 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>-10.22977594714139</v>
+        <v>-8.27046086153832</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>-9.491095626764828</v>
+        <v>-7.829235398752177</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-9.916492826413048</v>
+        <v>-11.59769813512834</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-17.24162460175855</v>
+        <v>-16.82316437603692</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-10.16119400565093</v>
+        <v>-9.902442819617502</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>-12.36013269677786</v>
+        <v>-11.32820450068329</v>
       </c>
     </row>
     <row r="11">
@@ -787,22 +787,22 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>-15.70197596281848</v>
+        <v>-14.34930357375794</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>-17.49875586310411</v>
+        <v>-15.61167050968604</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>-16.23195960796362</v>
+        <v>-17.49266175697551</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>-24.05417742507901</v>
+        <v>-23.40112686692987</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-14.27290778062123</v>
+        <v>-13.70522320936908</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-18.08260311179781</v>
+        <v>-16.46153011126313</v>
       </c>
     </row>
     <row r="12">
@@ -813,22 +813,22 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>-4.000376586760974</v>
+        <v>-2.916236969959481</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>-1.284970466871025</v>
+        <v>-0.2300195780235102</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-3.392458528922234</v>
+        <v>-6.404642735607922</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>-9.883902513915206</v>
+        <v>-9.4362662410081</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-5.67343292262395</v>
+        <v>-5.852056817527771</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>-6.217136865222046</v>
+        <v>-5.841727056488352</v>
       </c>
     </row>
     <row r="13">
@@ -839,22 +839,22 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>-0.1874354894981128</v>
+        <v>-0.1563928263784801</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>-0.1739009890214828</v>
+        <v>-0.1480493376236778</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>-0.2214858217580708</v>
+        <v>-0.2587894564209809</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>-0.3850933450174213</v>
+        <v>-0.3753897983401193</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.2036506305793707</v>
+        <v>-0.2019876828312327</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.2477217555676677</v>
+        <v>-0.2310700318509633</v>
       </c>
     </row>
     <row r="14">
@@ -865,22 +865,22 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>-0.2800839536070972</v>
+        <v>-0.2518657688169734</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>-0.3036301343995843</v>
+        <v>-0.2851692171687693</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>-0.335771249555151</v>
+        <v>-0.3622857870512979</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-0.508876701436594</v>
+        <v>-0.5016257873386282</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.2735183167357972</v>
+        <v>-0.2683524225511442</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.3482704303248685</v>
+        <v>-0.327501321657317</v>
       </c>
     </row>
     <row r="15">
@@ -891,22 +891,22 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>-0.08108628331450166</v>
+        <v>-0.05601534463156317</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>-0.02345659761489161</v>
+        <v>-0.004335273991666654</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>-0.07760648436282587</v>
+        <v>-0.1487704823175333</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>-0.2286483413558958</v>
+        <v>-0.2158891125144077</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.1175882916795651</v>
+        <v>-0.1248864973812781</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.1282189479149009</v>
+        <v>-0.1217621453480269</v>
       </c>
     </row>
     <row r="16">
@@ -921,22 +921,22 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>-7.610050152512465</v>
+        <v>-7.337544583071898</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>-23.75876352064948</v>
+        <v>-23.0059449053007</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>-12.71822701762091</v>
+        <v>-10.06060657520428</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>-14.14471555302154</v>
+        <v>-13.9943082214331</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-9.946138391701902</v>
+        <v>-8.458606141869945</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>-18.96886265521468</v>
+        <v>-18.47501226520008</v>
       </c>
     </row>
     <row r="17">
@@ -947,22 +947,22 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>-18.71928173642811</v>
+        <v>-16.77936561450072</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>-35.4779983254945</v>
+        <v>-33.83633379558465</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>-22.5607162130729</v>
+        <v>-19.61054209423214</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>-26.04059599049608</v>
+        <v>-25.65807053232232</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-17.17018843119912</v>
+        <v>-14.87225473676951</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-26.84499736029849</v>
+        <v>-25.73916359987038</v>
       </c>
     </row>
     <row r="18">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>3.186342780286502</v>
+        <v>1.785424471336478</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>-10.71646260846286</v>
+        <v>-9.522131838627878</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>-1.745389706153557</v>
+        <v>-0.6452548724987804</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>-2.514145062443085</v>
+        <v>-1.484984908530047</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-1.353250599069958</v>
+        <v>-1.572627437047151</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>-9.94453613078675</v>
+        <v>-8.929299583621095</v>
       </c>
     </row>
     <row r="19">
@@ -999,22 +999,22 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>-0.1439182569480047</v>
+        <v>-0.1402334300247062</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>-0.4493163336121799</v>
+        <v>-0.439684219769206</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>-0.3000294687673161</v>
+        <v>-0.2365594550052095</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>-0.3336810616258132</v>
+        <v>-0.3290543071425011</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.2086935155335914</v>
+        <v>-0.1783896281146383</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.398011617905231</v>
+        <v>-0.3896328203636908</v>
       </c>
     </row>
     <row r="20">
@@ -1025,22 +1025,22 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>-0.3198176715701634</v>
+        <v>-0.2922157720624265</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>-0.6237125194410268</v>
+        <v>-0.6090716052042102</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>-0.4808562558655038</v>
+        <v>-0.4037160085709582</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>-0.5520725370335484</v>
+        <v>-0.5466501739851359</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.3345177886532594</v>
+        <v>-0.2990947041889519</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.537363985895559</v>
+        <v>-0.5248488305502942</v>
       </c>
     </row>
     <row r="21">
@@ -1051,22 +1051,22 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>0.06822991952877665</v>
+        <v>0.03787645706616159</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>-0.215779748429904</v>
+        <v>-0.2111925449274047</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>-0.05194880300806898</v>
+        <v>-0.01226447532487424</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>-0.06155024915157736</v>
+        <v>-0.03677120663528523</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-0.02672042714669766</v>
+        <v>-0.03808368385913938</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-0.2277833883068105</v>
+        <v>-0.2009580920368715</v>
       </c>
     </row>
     <row r="22">
@@ -1081,22 +1081,22 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>-8.391661179470066</v>
+        <v>-7.012123389797709</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>-12.66656231669381</v>
+        <v>-10.92451973969186</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>-10.25460147098062</v>
+        <v>-10.70933135887874</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>-17.22004337494615</v>
+        <v>-16.20408925909721</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-9.222914364735846</v>
+        <v>-8.703078234830148</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-14.29230862135718</v>
+        <v>-12.95984016348431</v>
       </c>
     </row>
     <row r="23">
@@ -1107,22 +1107,22 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>-13.07779820245377</v>
+        <v>-11.79280694951154</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>-18.75993225146343</v>
+        <v>-16.89269946741019</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>-15.40815857156266</v>
+        <v>-15.40827692272912</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>-22.8758099286172</v>
+        <v>-21.86613755299545</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-12.90848333589963</v>
+        <v>-12.11384485314412</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>-18.78266628656673</v>
+        <v>-17.11730323954491</v>
       </c>
     </row>
     <row r="24">
@@ -1133,22 +1133,22 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>-2.950330811214615</v>
+        <v>-2.76166097031132</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>-6.187606656587176</v>
+        <v>-4.282997047965295</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>-5.419832303612407</v>
+        <v>-5.954766706598869</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>-10.2878553892248</v>
+        <v>-10.55120843513258</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-5.712606164043647</v>
+        <v>-5.295262312468996</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>-9.696161862916217</v>
+        <v>-8.443330009327685</v>
       </c>
     </row>
     <row r="25">
@@ -1159,22 +1159,22 @@
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>-0.1561113057524038</v>
+        <v>-0.1348640875302088</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>-0.2356379196399032</v>
+        <v>-0.2101111609848326</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>-0.2276652148271062</v>
+        <v>-0.2389945580816009</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>-0.3823068975799315</v>
+        <v>-0.3616182020908372</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.1863526481968759</v>
+        <v>-0.1794916767871277</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.2887817727789596</v>
+        <v>-0.2672828370687811</v>
       </c>
     </row>
     <row r="26">
@@ -1185,22 +1185,22 @@
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>-0.2387043366567352</v>
+        <v>-0.2189998631388368</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>-0.3436109249951637</v>
+        <v>-0.3127172273067742</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>-0.329164891411815</v>
+        <v>-0.3268659071585072</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>-0.4853599544127974</v>
+        <v>-0.4691938580818688</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.2515365723429265</v>
+        <v>-0.2430852991063185</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.3702867044997458</v>
+        <v>-0.3433096968383971</v>
       </c>
     </row>
     <row r="27">
@@ -1211,22 +1211,22 @@
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>-0.05911705144765615</v>
+        <v>-0.05717056304822063</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>-0.122518135302151</v>
+        <v>-0.08233093206123655</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>-0.1280573769471604</v>
+        <v>-0.1412282835570448</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>-0.2389020887040406</v>
+        <v>-0.2377393379682083</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-0.119731746597375</v>
+        <v>-0.1112846124472975</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.1993494072630917</v>
+        <v>-0.1793936582315757</v>
       </c>
     </row>
     <row r="28">
